--- a/_static/global/ids_party.xlsx
+++ b/_static/global/ids_party.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chbuschi\Documents\Research\Group Memory\Otree\Memory\_static\global\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48760123-3908-4B16-9B4A-FD14C037CD70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FBEDFC-9E49-40BA-A8C5-5C1311541782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23400" yWindow="2985" windowWidth="21600" windowHeight="12525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
     <t>logic</t>
   </si>
   <si>
-    <t>effort</t>
-  </si>
-  <si>
     <t>luck</t>
   </si>
   <si>
@@ -456,9 +453,6 @@
     <t>logic_sign_shown</t>
   </si>
   <si>
-    <t>beliefs_ref</t>
-  </si>
-  <si>
     <t>ingroup</t>
   </si>
   <si>
@@ -468,9 +462,6 @@
     <t xml:space="preserve">ingroup </t>
   </si>
   <si>
-    <t>beliefs_example_value</t>
-  </si>
-  <si>
     <t>low</t>
   </si>
   <si>
@@ -484,6 +475,15 @@
   </si>
   <si>
     <t>under</t>
+  </si>
+  <si>
+    <t>BeliefsNoMemory</t>
+  </si>
+  <si>
+    <t>belief_ref</t>
+  </si>
+  <si>
+    <t>belief_example_value</t>
   </si>
 </sst>
 </file>
@@ -840,33 +840,33 @@
         <v>7</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="I1" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -875,80 +875,80 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L3" t="s">
+        <v>146</v>
+      </c>
+      <c r="M3" t="s">
         <v>149</v>
-      </c>
-      <c r="M3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -963,39 +963,39 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="G4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K4" t="s">
+        <v>143</v>
+      </c>
+      <c r="L4" t="s">
         <v>145</v>
       </c>
-      <c r="L4" t="s">
-        <v>148</v>
-      </c>
       <c r="M4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
@@ -1004,33 +1004,33 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
@@ -1045,33 +1045,33 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K6" t="s">
+        <v>143</v>
+      </c>
+      <c r="L6" t="s">
         <v>145</v>
       </c>
-      <c r="L6" t="s">
-        <v>148</v>
-      </c>
       <c r="M6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -1080,45 +1080,45 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K7" t="s">
+        <v>143</v>
+      </c>
+      <c r="L7" t="s">
         <v>145</v>
       </c>
-      <c r="L7" t="s">
-        <v>148</v>
-      </c>
       <c r="M7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
@@ -1127,33 +1127,33 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L8" t="s">
+        <v>146</v>
+      </c>
+      <c r="M8" t="s">
         <v>149</v>
-      </c>
-      <c r="M8" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
@@ -1162,80 +1162,80 @@
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K9" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L9" t="s">
+        <v>146</v>
+      </c>
+      <c r="M9" t="s">
         <v>149</v>
-      </c>
-      <c r="M9" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
         <v>8</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
         <v>2</v>
@@ -1244,39 +1244,39 @@
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L11" t="s">
+        <v>146</v>
+      </c>
+      <c r="M11" t="s">
         <v>149</v>
-      </c>
-      <c r="M11" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
         <v>2</v>
@@ -1291,80 +1291,80 @@
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K12" t="s">
+        <v>143</v>
+      </c>
+      <c r="L12" t="s">
         <v>145</v>
       </c>
-      <c r="L12" t="s">
-        <v>148</v>
-      </c>
       <c r="M12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s">
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L13" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M13" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
@@ -1373,115 +1373,115 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K14" t="s">
+        <v>143</v>
+      </c>
+      <c r="L14" t="s">
         <v>145</v>
       </c>
-      <c r="L14" t="s">
-        <v>148</v>
-      </c>
       <c r="M14" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K15" t="s">
+        <v>143</v>
+      </c>
+      <c r="L15" t="s">
         <v>145</v>
       </c>
-      <c r="L15" t="s">
-        <v>148</v>
-      </c>
       <c r="M15" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
         <v>2</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L16" t="s">
+        <v>146</v>
+      </c>
+      <c r="M16" t="s">
         <v>149</v>
-      </c>
-      <c r="M16" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
         <v>1</v>
@@ -1496,33 +1496,33 @@
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K17" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L17" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M17" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
         <v>2</v>
@@ -1534,36 +1534,36 @@
         <v>8</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L18" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M18" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
         <v>1</v>
@@ -1572,39 +1572,39 @@
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K19" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L19" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M19" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
         <v>2</v>
@@ -1613,39 +1613,39 @@
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="G20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L20" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M20" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
         <v>1</v>
@@ -1654,39 +1654,39 @@
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L21" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M21" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
         <v>1</v>
@@ -1695,39 +1695,39 @@
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E22" t="s">
         <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K22" t="s">
+        <v>143</v>
+      </c>
+      <c r="L22" t="s">
         <v>145</v>
       </c>
-      <c r="L22" t="s">
-        <v>148</v>
-      </c>
       <c r="M22" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B23" t="s">
         <v>1</v>
@@ -1742,33 +1742,33 @@
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K23" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L23" t="s">
+        <v>146</v>
+      </c>
+      <c r="M23" t="s">
         <v>149</v>
-      </c>
-      <c r="M23" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
         <v>1</v>
@@ -1777,80 +1777,80 @@
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K24" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L24" t="s">
+        <v>146</v>
+      </c>
+      <c r="M24" t="s">
         <v>149</v>
-      </c>
-      <c r="M24" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K25" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L25" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M25" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B26" t="s">
         <v>2</v>
@@ -1859,39 +1859,39 @@
         <v>3</v>
       </c>
       <c r="D26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K26" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L26" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M26" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s">
         <v>2</v>
@@ -1906,74 +1906,74 @@
         <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K27" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L27" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M27" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L28" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M28" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B29" t="s">
         <v>2</v>
@@ -1988,33 +1988,33 @@
         <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L29" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B30" t="s">
         <v>2</v>
@@ -2026,36 +2026,36 @@
         <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K30" t="s">
+        <v>143</v>
+      </c>
+      <c r="L30" t="s">
         <v>145</v>
       </c>
-      <c r="L30" t="s">
-        <v>148</v>
-      </c>
       <c r="M30" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
         <v>1</v>
@@ -2064,39 +2064,39 @@
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L31" t="s">
+        <v>146</v>
+      </c>
+      <c r="M31" t="s">
         <v>149</v>
-      </c>
-      <c r="M31" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B32" t="s">
         <v>2</v>
@@ -2105,39 +2105,39 @@
         <v>3</v>
       </c>
       <c r="D32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K32" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L32" t="s">
+        <v>146</v>
+      </c>
+      <c r="M32" t="s">
         <v>149</v>
-      </c>
-      <c r="M32" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B33" t="s">
         <v>2</v>
@@ -2149,36 +2149,36 @@
         <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K33" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L33" t="s">
+        <v>146</v>
+      </c>
+      <c r="M33" t="s">
         <v>149</v>
-      </c>
-      <c r="M33" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B34" t="s">
         <v>2</v>
@@ -2187,45 +2187,45 @@
         <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K34" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L34" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M34" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B35" t="s">
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D35" t="s">
         <v>8</v>
@@ -2234,33 +2234,33 @@
         <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L35" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M35" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
         <v>1</v>
@@ -2269,39 +2269,39 @@
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E36" t="s">
         <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K36" t="s">
+        <v>143</v>
+      </c>
+      <c r="L36" t="s">
         <v>145</v>
       </c>
-      <c r="L36" t="s">
-        <v>148</v>
-      </c>
       <c r="M36" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
         <v>2</v>
@@ -2310,80 +2310,80 @@
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K37" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L37" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M37" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E38" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="G38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K38" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L38" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M38" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B39" t="s">
         <v>2</v>
@@ -2392,39 +2392,39 @@
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="G39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L39" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M39" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B40" t="s">
         <v>1</v>
@@ -2436,36 +2436,36 @@
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K40" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L40" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M40" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B41" t="s">
         <v>2</v>
@@ -2474,80 +2474,80 @@
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L41" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M41" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B42" t="s">
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K42" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L42" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M42" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
         <v>1</v>
@@ -2556,39 +2556,39 @@
         <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K43" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L43" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M43" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
         <v>1</v>
@@ -2597,121 +2597,121 @@
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K44" t="s">
+        <v>143</v>
+      </c>
+      <c r="L44" t="s">
         <v>145</v>
       </c>
-      <c r="L44" t="s">
-        <v>148</v>
-      </c>
       <c r="M44" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B45" t="s">
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E45" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K45" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L45" t="s">
+        <v>146</v>
+      </c>
+      <c r="M45" t="s">
         <v>149</v>
-      </c>
-      <c r="M45" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E46" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F46" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K46" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L46" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M46" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B47" t="s">
         <v>1</v>
@@ -2726,33 +2726,33 @@
         <v>9</v>
       </c>
       <c r="F47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K47" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L47" t="s">
+        <v>146</v>
+      </c>
+      <c r="M47" t="s">
         <v>149</v>
-      </c>
-      <c r="M47" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B48" t="s">
         <v>1</v>
@@ -2761,39 +2761,39 @@
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K48" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L48" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M48" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B49" t="s">
         <v>1</v>
@@ -2802,39 +2802,39 @@
         <v>3</v>
       </c>
       <c r="D49" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L49" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M49" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B50" t="s">
         <v>1</v>
@@ -2846,36 +2846,36 @@
         <v>9</v>
       </c>
       <c r="E50" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K50" t="s">
+        <v>143</v>
+      </c>
+      <c r="L50" t="s">
         <v>145</v>
       </c>
-      <c r="L50" t="s">
-        <v>148</v>
-      </c>
       <c r="M50" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B51" t="s">
         <v>1</v>
@@ -2884,80 +2884,80 @@
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K51" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L51" t="s">
+        <v>146</v>
+      </c>
+      <c r="M51" t="s">
         <v>149</v>
-      </c>
-      <c r="M51" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B52" t="s">
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K52" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L52" t="s">
+        <v>146</v>
+      </c>
+      <c r="M52" t="s">
         <v>149</v>
-      </c>
-      <c r="M52" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B53" t="s">
         <v>1</v>
@@ -2972,33 +2972,33 @@
         <v>9</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L53" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M53" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B54" t="s">
         <v>1</v>
@@ -3007,39 +3007,39 @@
         <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E54" t="s">
         <v>9</v>
       </c>
       <c r="F54" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L54" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M54" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B55" t="s">
         <v>1</v>
@@ -3048,39 +3048,39 @@
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E55" t="s">
         <v>9</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="G55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K55" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L55" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M55" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B56" t="s">
         <v>1</v>
@@ -3089,127 +3089,127 @@
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E56" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F56" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="G56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K56" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L56" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M56" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B57" t="s">
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K57" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L57" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M57" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B58" t="s">
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E58" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I58" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K58" t="s">
+        <v>143</v>
+      </c>
+      <c r="L58" t="s">
         <v>145</v>
       </c>
-      <c r="L58" t="s">
-        <v>148</v>
-      </c>
       <c r="M58" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B59" t="s">
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D59" t="s">
         <v>9</v>
@@ -3218,74 +3218,74 @@
         <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K59" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L59" t="s">
+        <v>146</v>
+      </c>
+      <c r="M59" t="s">
         <v>149</v>
-      </c>
-      <c r="M59" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B60" t="s">
         <v>1</v>
       </c>
       <c r="C60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H60" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J60" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K60" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L60" t="s">
+        <v>146</v>
+      </c>
+      <c r="M60" t="s">
         <v>149</v>
-      </c>
-      <c r="M60" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B61" t="s">
         <v>2</v>
@@ -3300,33 +3300,33 @@
         <v>9</v>
       </c>
       <c r="F61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L61" t="s">
+        <v>146</v>
+      </c>
+      <c r="M61" t="s">
         <v>149</v>
-      </c>
-      <c r="M61" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B62" t="s">
         <v>2</v>
@@ -3335,80 +3335,80 @@
         <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E62" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F62" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L62" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M62" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B63" t="s">
         <v>1</v>
       </c>
       <c r="C63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E63" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F63" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K63" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L63" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M63" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B64" t="s">
         <v>1</v>
@@ -3423,33 +3423,33 @@
         <v>9</v>
       </c>
       <c r="F64" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="G64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K64" t="s">
+        <v>143</v>
+      </c>
+      <c r="L64" t="s">
         <v>145</v>
       </c>
-      <c r="L64" t="s">
-        <v>148</v>
-      </c>
       <c r="M64" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B65" t="s">
         <v>2</v>
@@ -3461,36 +3461,36 @@
         <v>9</v>
       </c>
       <c r="E65" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F65" t="s">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="G65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K65" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L65" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M65" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B66" t="s">
         <v>1</v>
@@ -3499,39 +3499,39 @@
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
       </c>
       <c r="F66" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K66" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L66" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M66" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B67" t="s">
         <v>1</v>
@@ -3543,36 +3543,36 @@
         <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="G67" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J67" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L67" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M67" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B68" t="s">
         <v>2</v>
@@ -3587,33 +3587,33 @@
         <v>8</v>
       </c>
       <c r="F68" t="s">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="G68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I68" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J68" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K68" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L68" t="s">
+        <v>146</v>
+      </c>
+      <c r="M68" t="s">
         <v>149</v>
-      </c>
-      <c r="M68" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B69" t="s">
         <v>1</v>
@@ -3625,36 +3625,36 @@
         <v>8</v>
       </c>
       <c r="E69" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F69" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K69" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L69" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M69" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B70" t="s">
         <v>2</v>
@@ -3666,77 +3666,77 @@
         <v>8</v>
       </c>
       <c r="E70" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F70" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I70" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J70" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L70" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M70" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B71" t="s">
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D71" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E71" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F71" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="G71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K71" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L71" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M71" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B72" t="s">
         <v>1</v>
@@ -3745,39 +3745,39 @@
         <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E72" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F72" t="s">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="G72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K72" t="s">
+        <v>143</v>
+      </c>
+      <c r="L72" t="s">
         <v>145</v>
       </c>
-      <c r="L72" t="s">
-        <v>148</v>
-      </c>
       <c r="M72" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B73" t="s">
         <v>1</v>
@@ -3792,33 +3792,33 @@
         <v>9</v>
       </c>
       <c r="F73" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K73" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L73" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M73" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B74" t="s">
         <v>1</v>
@@ -3833,33 +3833,33 @@
         <v>9</v>
       </c>
       <c r="F74" t="s">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="G74" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H74" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K74" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L74" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M74" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B75" t="s">
         <v>2</v>
@@ -3874,33 +3874,33 @@
         <v>8</v>
       </c>
       <c r="F75" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="G75" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H75" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I75" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J75" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K75" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L75" t="s">
+        <v>146</v>
+      </c>
+      <c r="M75" t="s">
         <v>149</v>
-      </c>
-      <c r="M75" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B76" t="s">
         <v>2</v>
@@ -3909,39 +3909,39 @@
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E76" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G76" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H76" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I76" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J76" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K76" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L76" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M76" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B77" t="s">
         <v>1</v>
@@ -3953,77 +3953,77 @@
         <v>9</v>
       </c>
       <c r="E77" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K77" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L77" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M77" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B78" t="s">
         <v>2</v>
       </c>
       <c r="C78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E78" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K78" t="s">
+        <v>143</v>
+      </c>
+      <c r="L78" t="s">
         <v>145</v>
       </c>
-      <c r="L78" t="s">
-        <v>148</v>
-      </c>
       <c r="M78" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B79" t="s">
         <v>1</v>
@@ -4032,45 +4032,45 @@
         <v>3</v>
       </c>
       <c r="D79" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E79" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F79" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G79" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H79" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I79" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J79" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K79" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L79" t="s">
+        <v>146</v>
+      </c>
+      <c r="M79" t="s">
         <v>149</v>
-      </c>
-      <c r="M79" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B80" t="s">
         <v>1</v>
       </c>
       <c r="C80" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D80" t="s">
         <v>8</v>
@@ -4079,33 +4079,33 @@
         <v>9</v>
       </c>
       <c r="F80" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G80" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H80" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I80" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J80" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K80" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L80" t="s">
+        <v>146</v>
+      </c>
+      <c r="M80" t="s">
         <v>149</v>
-      </c>
-      <c r="M80" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B81" t="s">
         <v>2</v>
@@ -4114,45 +4114,45 @@
         <v>3</v>
       </c>
       <c r="D81" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E81" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F81" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G81" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H81" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I81" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J81" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K81" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L81" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M81" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B82" t="s">
         <v>1</v>
       </c>
       <c r="C82" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D82" t="s">
         <v>8</v>
@@ -4161,33 +4161,33 @@
         <v>9</v>
       </c>
       <c r="F82" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G82" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H82" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I82" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J82" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K82" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L82" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M82" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B83" t="s">
         <v>1</v>
@@ -4196,39 +4196,39 @@
         <v>3</v>
       </c>
       <c r="D83" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E83" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G83" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H83" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I83" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J83" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K83" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L83" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M83" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B84" t="s">
         <v>1</v>
@@ -4237,80 +4237,80 @@
         <v>3</v>
       </c>
       <c r="D84" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
       </c>
       <c r="F84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G84" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H84" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I84" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J84" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K84" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L84" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M84" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B85" t="s">
         <v>1</v>
       </c>
       <c r="C85" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
       </c>
       <c r="F85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G85" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H85" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I85" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J85" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K85" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L85" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M85" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B86" t="s">
         <v>1</v>
@@ -4325,33 +4325,33 @@
         <v>8</v>
       </c>
       <c r="F86" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H86" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K86" t="s">
+        <v>143</v>
+      </c>
+      <c r="L86" t="s">
         <v>145</v>
       </c>
-      <c r="L86" t="s">
-        <v>148</v>
-      </c>
       <c r="M86" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B87" t="s">
         <v>1</v>
@@ -4360,39 +4360,39 @@
         <v>3</v>
       </c>
       <c r="D87" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E87" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F87" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G87" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H87" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I87" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J87" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K87" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L87" t="s">
+        <v>146</v>
+      </c>
+      <c r="M87" t="s">
         <v>149</v>
-      </c>
-      <c r="M87" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B88" t="s">
         <v>1</v>
@@ -4401,39 +4401,39 @@
         <v>3</v>
       </c>
       <c r="D88" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E88" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K88" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L88" t="s">
+        <v>146</v>
+      </c>
+      <c r="M88" t="s">
         <v>149</v>
-      </c>
-      <c r="M88" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B89" t="s">
         <v>2</v>
@@ -4445,36 +4445,36 @@
         <v>8</v>
       </c>
       <c r="E89" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F89" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G89" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H89" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I89" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J89" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K89" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L89" t="s">
+        <v>146</v>
+      </c>
+      <c r="M89" t="s">
         <v>149</v>
-      </c>
-      <c r="M89" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B90" t="s">
         <v>2</v>
@@ -4483,121 +4483,121 @@
         <v>3</v>
       </c>
       <c r="D90" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E90" t="s">
         <v>9</v>
       </c>
       <c r="F90" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G90" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H90" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I90" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J90" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K90" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L90" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M90" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B91" t="s">
         <v>2</v>
       </c>
       <c r="C91" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D91" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
       </c>
       <c r="F91" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G91" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H91" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I91" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J91" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K91" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L91" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M91" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B92" t="s">
         <v>2</v>
       </c>
       <c r="C92" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D92" t="s">
         <v>9</v>
       </c>
       <c r="E92" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F92" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H92" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K92" t="s">
+        <v>143</v>
+      </c>
+      <c r="L92" t="s">
         <v>145</v>
       </c>
-      <c r="L92" t="s">
-        <v>148</v>
-      </c>
       <c r="M92" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B93" t="s">
         <v>2</v>
@@ -4606,39 +4606,39 @@
         <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E93" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F93" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G93" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H93" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I93" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J93" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K93" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L93" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M93" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B94" t="s">
         <v>1</v>
@@ -4647,121 +4647,121 @@
         <v>3</v>
       </c>
       <c r="D94" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E94" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F94" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G94" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H94" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I94" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J94" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K94" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L94" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M94" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B95" t="s">
         <v>1</v>
       </c>
       <c r="C95" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D95" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E95" t="s">
         <v>9</v>
       </c>
       <c r="F95" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G95" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H95" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I95" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J95" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K95" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L95" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M95" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B96" t="s">
         <v>1</v>
       </c>
       <c r="C96" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D96" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E96" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F96" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G96" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H96" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I96" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J96" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K96" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L96" t="s">
+        <v>146</v>
+      </c>
+      <c r="M96" t="s">
         <v>149</v>
-      </c>
-      <c r="M96" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B97" t="s">
         <v>2</v>
@@ -4773,36 +4773,36 @@
         <v>8</v>
       </c>
       <c r="E97" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F97" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G97" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H97" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I97" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J97" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K97" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L97" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M97" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B98" t="s">
         <v>2</v>
@@ -4817,39 +4817,39 @@
         <v>9</v>
       </c>
       <c r="F98" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G98" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H98" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I98" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J98" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K98" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L98" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M98" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B99" t="s">
         <v>2</v>
       </c>
       <c r="C99" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D99" t="s">
         <v>9</v>
@@ -4858,33 +4858,33 @@
         <v>8</v>
       </c>
       <c r="F99" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G99" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H99" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I99" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J99" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K99" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L99" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M99" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B100" t="s">
         <v>1</v>
@@ -4893,80 +4893,80 @@
         <v>3</v>
       </c>
       <c r="D100" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E100" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F100" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G100" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H100" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I100" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J100" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K100" t="s">
+        <v>143</v>
+      </c>
+      <c r="L100" t="s">
         <v>145</v>
       </c>
-      <c r="L100" t="s">
-        <v>148</v>
-      </c>
       <c r="M100" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B101" t="s">
         <v>1</v>
       </c>
       <c r="C101" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D101" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E101" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F101" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G101" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I101" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J101" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K101" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L101" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M101" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B102" t="s">
         <v>2</v>
@@ -4975,39 +4975,39 @@
         <v>3</v>
       </c>
       <c r="D102" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E102" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F102" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G102" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H102" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I102" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J102" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K102" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L102" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M102" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B103" t="s">
         <v>2</v>
@@ -5016,39 +5016,39 @@
         <v>3</v>
       </c>
       <c r="D103" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E103" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F103" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G103" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H103" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I103" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J103" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K103" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L103" t="s">
+        <v>146</v>
+      </c>
+      <c r="M103" t="s">
         <v>149</v>
-      </c>
-      <c r="M103" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B104" t="s">
         <v>1</v>
@@ -5057,39 +5057,39 @@
         <v>3</v>
       </c>
       <c r="D104" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E104" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F104" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G104" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H104" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I104" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J104" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K104" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L104" t="s">
+        <v>146</v>
+      </c>
+      <c r="M104" t="s">
         <v>149</v>
-      </c>
-      <c r="M104" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B105" t="s">
         <v>2</v>
@@ -5098,39 +5098,39 @@
         <v>3</v>
       </c>
       <c r="D105" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E105" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F105" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G105" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H105" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I105" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J105" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K105" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L105" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M105" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B106" t="s">
         <v>2</v>
@@ -5139,39 +5139,39 @@
         <v>3</v>
       </c>
       <c r="D106" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E106" t="s">
         <v>9</v>
       </c>
       <c r="F106" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G106" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H106" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I106" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J106" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K106" t="s">
+        <v>143</v>
+      </c>
+      <c r="L106" t="s">
         <v>145</v>
       </c>
-      <c r="L106" t="s">
-        <v>148</v>
-      </c>
       <c r="M106" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B107" t="s">
         <v>2</v>
@@ -5180,39 +5180,39 @@
         <v>3</v>
       </c>
       <c r="D107" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E107" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F107" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G107" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H107" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I107" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J107" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K107" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L107" t="s">
+        <v>146</v>
+      </c>
+      <c r="M107" t="s">
         <v>149</v>
-      </c>
-      <c r="M107" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B108" t="s">
         <v>1</v>
@@ -5221,39 +5221,39 @@
         <v>3</v>
       </c>
       <c r="D108" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
       </c>
       <c r="F108" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G108" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H108" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I108" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J108" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K108" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L108" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M108" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B109" t="s">
         <v>2</v>
@@ -5262,39 +5262,39 @@
         <v>3</v>
       </c>
       <c r="D109" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F109" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G109" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H109" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I109" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J109" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K109" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L109" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M109" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B110" t="s">
         <v>2</v>
@@ -5309,74 +5309,74 @@
         <v>8</v>
       </c>
       <c r="F110" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G110" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H110" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I110" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J110" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K110" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L110" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M110" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B111" t="s">
         <v>1</v>
       </c>
       <c r="C111" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D111" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E111" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F111" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G111" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H111" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I111" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J111" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K111" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L111" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M111" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B112" t="s">
         <v>2</v>
@@ -5388,36 +5388,36 @@
         <v>8</v>
       </c>
       <c r="E112" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F112" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G112" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H112" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I112" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J112" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K112" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L112" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M112" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B113" t="s">
         <v>2</v>
@@ -5426,45 +5426,45 @@
         <v>3</v>
       </c>
       <c r="D113" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E113" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F113" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G113" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H113" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I113" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J113" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K113" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L113" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M113" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B114" t="s">
         <v>2</v>
       </c>
       <c r="C114" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D114" t="s">
         <v>8</v>
@@ -5473,39 +5473,39 @@
         <v>9</v>
       </c>
       <c r="F114" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G114" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H114" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I114" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J114" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K114" t="s">
+        <v>143</v>
+      </c>
+      <c r="L114" t="s">
         <v>145</v>
       </c>
-      <c r="L114" t="s">
-        <v>148</v>
-      </c>
       <c r="M114" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B115" t="s">
         <v>1</v>
       </c>
       <c r="C115" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D115" t="s">
         <v>9</v>
@@ -5514,33 +5514,33 @@
         <v>8</v>
       </c>
       <c r="F115" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G115" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H115" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I115" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J115" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K115" t="s">
+        <v>143</v>
+      </c>
+      <c r="L115" t="s">
         <v>145</v>
       </c>
-      <c r="L115" t="s">
-        <v>148</v>
-      </c>
       <c r="M115" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B116" t="s">
         <v>2</v>
@@ -5549,39 +5549,39 @@
         <v>3</v>
       </c>
       <c r="D116" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E116" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F116" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G116" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H116" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I116" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J116" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K116" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L116" t="s">
+        <v>146</v>
+      </c>
+      <c r="M116" t="s">
         <v>149</v>
-      </c>
-      <c r="M116" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B117" t="s">
         <v>2</v>
@@ -5596,74 +5596,74 @@
         <v>8</v>
       </c>
       <c r="F117" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G117" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H117" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I117" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J117" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K117" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L117" t="s">
+        <v>146</v>
+      </c>
+      <c r="M117" t="s">
         <v>149</v>
-      </c>
-      <c r="M117" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B118" t="s">
         <v>1</v>
       </c>
       <c r="C118" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D118" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E118" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F118" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G118" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H118" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I118" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J118" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K118" t="s">
+        <v>143</v>
+      </c>
+      <c r="L118" t="s">
         <v>145</v>
       </c>
-      <c r="L118" t="s">
-        <v>148</v>
-      </c>
       <c r="M118" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B119" t="s">
         <v>2</v>
@@ -5672,39 +5672,39 @@
         <v>3</v>
       </c>
       <c r="D119" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E119" t="s">
         <v>9</v>
       </c>
       <c r="F119" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G119" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H119" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I119" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J119" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K119" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L119" t="s">
+        <v>146</v>
+      </c>
+      <c r="M119" t="s">
         <v>149</v>
-      </c>
-      <c r="M119" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B120" t="s">
         <v>2</v>
@@ -5713,80 +5713,80 @@
         <v>3</v>
       </c>
       <c r="D120" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E120" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F120" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G120" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H120" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I120" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J120" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K120" t="s">
+        <v>143</v>
+      </c>
+      <c r="L120" t="s">
         <v>145</v>
       </c>
-      <c r="L120" t="s">
-        <v>148</v>
-      </c>
       <c r="M120" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B121" t="s">
         <v>1</v>
       </c>
       <c r="C121" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D121" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E121" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F121" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G121" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H121" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I121" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J121" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K121" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L121" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M121" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B122" t="s">
         <v>2</v>
@@ -5795,34 +5795,34 @@
         <v>3</v>
       </c>
       <c r="D122" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E122" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F122" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G122" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H122" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I122" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J122" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K122" t="s">
+        <v>143</v>
+      </c>
+      <c r="L122" t="s">
         <v>145</v>
       </c>
-      <c r="L122" t="s">
-        <v>148</v>
-      </c>
       <c r="M122" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/_static/global/ids_party.xlsx
+++ b/_static/global/ids_party.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chbuschi\Documents\Research\Group Memory\Otree\Memory\_static\global\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA96AC0-E587-437E-8432-A9169CE1F38A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A964C07E-3EAF-46AD-BC8F-CC6272901E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2418" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="230">
   <si>
     <t>prolificid</t>
   </si>
@@ -670,6 +670,51 @@
   </si>
   <si>
     <t>67f1f1d53b5c101545b04cfc</t>
+  </si>
+  <si>
+    <t>67f015260f679212b3c34caa</t>
+  </si>
+  <si>
+    <t>67d21364aa4dc87ecd8f3f1b</t>
+  </si>
+  <si>
+    <t>671c6fad5a9935e94b3025fd</t>
+  </si>
+  <si>
+    <t>645906dc264ac9eb66b7f3ec</t>
+  </si>
+  <si>
+    <t>67f1b8abe144ffdfc27d371a</t>
+  </si>
+  <si>
+    <t>58a1fe40ea3d11000170d9b9</t>
+  </si>
+  <si>
+    <t>67eafb930e75699288e09213</t>
+  </si>
+  <si>
+    <t>66d9fc2d2b46f520118ea65f</t>
+  </si>
+  <si>
+    <t>67f0e20347eb50d095c3866d</t>
+  </si>
+  <si>
+    <t>67217a2f6476292bf82e2e6d</t>
+  </si>
+  <si>
+    <t>67839a9f3657ad5351a92bb6</t>
+  </si>
+  <si>
+    <t>67722aa65639cba87301c81c</t>
+  </si>
+  <si>
+    <t>67e7dbf60ed0916f30880498</t>
+  </si>
+  <si>
+    <t>67e065974c85fbeb5f9f43be</t>
+  </si>
+  <si>
+    <t>687e30216d4ae341a5f8d2f1</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +1051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M186"/>
+  <dimension ref="A1:M201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
@@ -1667,7 +1712,7 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>215</v>
       </c>
       <c r="B17" t="s">
         <v>2</v>
@@ -1676,19 +1721,19 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I17" t="s">
         <v>15</v>
@@ -1697,21 +1742,21 @@
         <v>16</v>
       </c>
       <c r="K17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L17" t="s">
         <v>23</v>
       </c>
       <c r="M17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="s">
         <v>3</v>
@@ -1723,13 +1768,13 @@
         <v>9</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I18" t="s">
         <v>15</v>
@@ -1738,51 +1783,51 @@
         <v>16</v>
       </c>
       <c r="K18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="s">
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J19" t="s">
         <v>16</v>
       </c>
       <c r="K19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M19" t="s">
         <v>25</v>
@@ -1790,7 +1835,7 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
         <v>2</v>
@@ -1799,101 +1844,101 @@
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G20" t="s">
         <v>16</v>
       </c>
       <c r="H20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I20" t="s">
         <v>16</v>
       </c>
       <c r="J20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="s">
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="s">
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I22" t="s">
         <v>15</v>
@@ -1902,21 +1947,21 @@
         <v>16</v>
       </c>
       <c r="K22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="s">
         <v>3</v>
@@ -1928,48 +1973,48 @@
         <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23" t="s">
         <v>16</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K23" t="s">
         <v>20</v>
       </c>
       <c r="L23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" t="s">
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G24" t="s">
         <v>16</v>
@@ -1984,18 +2029,18 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L24" t="s">
         <v>23</v>
       </c>
       <c r="M24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
         <v>2</v>
@@ -2004,83 +2049,83 @@
         <v>3</v>
       </c>
       <c r="D25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
       </c>
       <c r="I25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J25" t="s">
         <v>15</v>
       </c>
       <c r="K25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="s">
         <v>3</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
       </c>
       <c r="I26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="s">
         <v>3</v>
@@ -2092,22 +2137,22 @@
         <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L27" t="s">
         <v>23</v>
@@ -2118,10 +2163,10 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="s">
         <v>3</v>
@@ -2133,36 +2178,36 @@
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G28" t="s">
         <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J28" t="s">
         <v>15</v>
       </c>
       <c r="K28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="s">
         <v>3</v>
@@ -2174,33 +2219,33 @@
         <v>8</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J29" t="s">
         <v>15</v>
       </c>
       <c r="K29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
         <v>2</v>
@@ -2209,16 +2254,16 @@
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -2230,7 +2275,7 @@
         <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L30" t="s">
         <v>23</v>
@@ -2241,7 +2286,7 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B31" t="s">
         <v>2</v>
@@ -2256,7 +2301,7 @@
         <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G31" t="s">
         <v>16</v>
@@ -2265,57 +2310,57 @@
         <v>15</v>
       </c>
       <c r="I31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L31" t="s">
         <v>23</v>
       </c>
       <c r="M31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="s">
         <v>3</v>
       </c>
       <c r="D32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M32" t="s">
         <v>25</v>
@@ -2323,7 +2368,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B33" t="s">
         <v>1</v>
@@ -2338,7 +2383,7 @@
         <v>8</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G33" t="s">
         <v>15</v>
@@ -2350,36 +2395,36 @@
         <v>15</v>
       </c>
       <c r="J33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L33" t="s">
         <v>22</v>
       </c>
       <c r="M33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" t="s">
         <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G34" t="s">
         <v>15</v>
@@ -2397,7 +2442,7 @@
         <v>20</v>
       </c>
       <c r="L34" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M34" t="s">
         <v>26</v>
@@ -2405,10 +2450,10 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B35" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" t="s">
         <v>3</v>
@@ -2420,7 +2465,7 @@
         <v>9</v>
       </c>
       <c r="F35" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
@@ -2432,7 +2477,7 @@
         <v>15</v>
       </c>
       <c r="J35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K35" t="s">
         <v>20</v>
@@ -2446,7 +2491,7 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>216</v>
       </c>
       <c r="B36" t="s">
         <v>1</v>
@@ -2455,13 +2500,13 @@
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
@@ -2470,7 +2515,7 @@
         <v>16</v>
       </c>
       <c r="I36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J36" t="s">
         <v>16</v>
@@ -2479,7 +2524,7 @@
         <v>21</v>
       </c>
       <c r="L36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M36" t="s">
         <v>26</v>
@@ -2487,28 +2532,28 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" t="s">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F37" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G37" t="s">
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I37" t="s">
         <v>15</v>
@@ -2528,7 +2573,7 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
         <v>1</v>
@@ -2537,10 +2582,10 @@
         <v>3</v>
       </c>
       <c r="D38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E38" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
         <v>12</v>
@@ -2549,19 +2594,19 @@
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M38" t="s">
         <v>26</v>
@@ -2569,37 +2614,37 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B39" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" t="s">
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
         <v>11</v>
       </c>
       <c r="G39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
       </c>
       <c r="I39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L39" t="s">
         <v>23</v>
@@ -2610,34 +2655,34 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" t="s">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G40" t="s">
         <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I40" t="s">
         <v>16</v>
       </c>
       <c r="J40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K40" t="s">
         <v>20</v>
@@ -2646,15 +2691,15 @@
         <v>22</v>
       </c>
       <c r="M40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B41" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="s">
         <v>3</v>
@@ -2666,7 +2711,7 @@
         <v>9</v>
       </c>
       <c r="F41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G41" t="s">
         <v>16</v>
@@ -2675,7 +2720,7 @@
         <v>15</v>
       </c>
       <c r="I41" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J41" t="s">
         <v>15</v>
@@ -2684,7 +2729,7 @@
         <v>21</v>
       </c>
       <c r="L41" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M41" t="s">
         <v>26</v>
@@ -2692,7 +2737,7 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B42" t="s">
         <v>2</v>
@@ -2701,13 +2746,13 @@
         <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G42" t="s">
         <v>15</v>
@@ -2716,7 +2761,7 @@
         <v>16</v>
       </c>
       <c r="I42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J42" t="s">
         <v>16</v>
@@ -2728,12 +2773,12 @@
         <v>22</v>
       </c>
       <c r="M42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B43" t="s">
         <v>2</v>
@@ -2748,7 +2793,7 @@
         <v>9</v>
       </c>
       <c r="F43" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G43" t="s">
         <v>16</v>
@@ -2757,7 +2802,7 @@
         <v>15</v>
       </c>
       <c r="I43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J43" t="s">
         <v>15</v>
@@ -2774,7 +2819,7 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B44" t="s">
         <v>2</v>
@@ -2789,7 +2834,7 @@
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G44" t="s">
         <v>15</v>
@@ -2798,7 +2843,7 @@
         <v>16</v>
       </c>
       <c r="I44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J44" t="s">
         <v>16</v>
@@ -2815,10 +2860,10 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B45" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="s">
         <v>3</v>
@@ -2830,19 +2875,19 @@
         <v>9</v>
       </c>
       <c r="F45" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G45" t="s">
         <v>16</v>
       </c>
       <c r="H45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I45" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K45" t="s">
         <v>21</v>
@@ -2851,12 +2896,12 @@
         <v>22</v>
       </c>
       <c r="M45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B46" t="s">
         <v>2</v>
@@ -2871,16 +2916,16 @@
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
       </c>
       <c r="I46" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J46" t="s">
         <v>16</v>
@@ -2889,7 +2934,7 @@
         <v>20</v>
       </c>
       <c r="L46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M46" t="s">
         <v>26</v>
@@ -2897,7 +2942,7 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B47" t="s">
         <v>1</v>
@@ -2912,7 +2957,7 @@
         <v>9</v>
       </c>
       <c r="F47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G47" t="s">
         <v>16</v>
@@ -2921,7 +2966,7 @@
         <v>16</v>
       </c>
       <c r="I47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J47" t="s">
         <v>16</v>
@@ -2938,7 +2983,7 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B48" t="s">
         <v>2</v>
@@ -2947,22 +2992,22 @@
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G48" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
       </c>
       <c r="I48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J48" t="s">
         <v>16</v>
@@ -2971,18 +3016,18 @@
         <v>20</v>
       </c>
       <c r="L48" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B49" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49" t="s">
         <v>3</v>
@@ -2994,16 +3039,16 @@
         <v>9</v>
       </c>
       <c r="F49" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G49" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
       </c>
       <c r="I49" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J49" t="s">
         <v>16</v>
@@ -3012,7 +3057,7 @@
         <v>21</v>
       </c>
       <c r="L49" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M49" t="s">
         <v>25</v>
@@ -3020,31 +3065,31 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B50" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" t="s">
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E50" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G50" t="s">
         <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I50" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J50" t="s">
         <v>16</v>
@@ -3061,7 +3106,7 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B51" t="s">
         <v>2</v>
@@ -3070,13 +3115,13 @@
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E51" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F51" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G51" t="s">
         <v>15</v>
@@ -3094,56 +3139,56 @@
         <v>21</v>
       </c>
       <c r="L51" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B52" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" t="s">
         <v>3</v>
       </c>
       <c r="D52" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E52" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J52" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K52" t="s">
         <v>20</v>
       </c>
       <c r="L52" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B53" t="s">
         <v>2</v>
@@ -3152,10 +3197,10 @@
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F53" t="s">
         <v>11</v>
@@ -3167,16 +3212,16 @@
         <v>16</v>
       </c>
       <c r="I53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J53" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L53" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M53" t="s">
         <v>26</v>
@@ -3184,7 +3229,7 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B54" t="s">
         <v>2</v>
@@ -3199,10 +3244,10 @@
         <v>9</v>
       </c>
       <c r="F54" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G54" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H54" t="s">
         <v>16</v>
@@ -3211,13 +3256,13 @@
         <v>16</v>
       </c>
       <c r="J54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K54" t="s">
         <v>20</v>
       </c>
       <c r="L54" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M54" t="s">
         <v>26</v>
@@ -3225,7 +3270,7 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B55" t="s">
         <v>2</v>
@@ -3234,16 +3279,16 @@
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E55" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F55" t="s">
         <v>11</v>
       </c>
       <c r="G55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H55" t="s">
         <v>16</v>
@@ -3255,18 +3300,18 @@
         <v>15</v>
       </c>
       <c r="K55" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L55" t="s">
         <v>23</v>
       </c>
       <c r="M55" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B56" t="s">
         <v>2</v>
@@ -3275,19 +3320,19 @@
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E56" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F56" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G56" t="s">
         <v>15</v>
       </c>
       <c r="H56" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I56" t="s">
         <v>16</v>
@@ -3299,7 +3344,7 @@
         <v>20</v>
       </c>
       <c r="L56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M56" t="s">
         <v>26</v>
@@ -3307,19 +3352,19 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B57" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" t="s">
         <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E57" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F57" t="s">
         <v>11</v>
@@ -3331,24 +3376,24 @@
         <v>16</v>
       </c>
       <c r="I57" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L57" t="s">
         <v>23</v>
       </c>
       <c r="M57" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B58" t="s">
         <v>2</v>
@@ -3357,10 +3402,10 @@
         <v>3</v>
       </c>
       <c r="D58" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F58" t="s">
         <v>27</v>
@@ -3378,7 +3423,7 @@
         <v>16</v>
       </c>
       <c r="K58" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L58" t="s">
         <v>23</v>
@@ -3389,40 +3434,40 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B59" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" t="s">
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E59" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F59" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G59" t="s">
         <v>16</v>
       </c>
       <c r="H59" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I59" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J59" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K59" t="s">
         <v>20</v>
       </c>
       <c r="L59" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M59" t="s">
         <v>26</v>
@@ -3430,7 +3475,7 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B60" t="s">
         <v>2</v>
@@ -3439,31 +3484,31 @@
         <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E60" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F60" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G60" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
       </c>
       <c r="I60" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J60" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K60" t="s">
         <v>21</v>
       </c>
       <c r="L60" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M60" t="s">
         <v>26</v>
@@ -3471,7 +3516,7 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B61" t="s">
         <v>2</v>
@@ -3480,19 +3525,19 @@
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F61" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G61" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I61" t="s">
         <v>16</v>
@@ -3507,42 +3552,42 @@
         <v>22</v>
       </c>
       <c r="M61" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B62" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" t="s">
         <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F62" t="s">
         <v>12</v>
       </c>
       <c r="G62" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L62" t="s">
         <v>22</v>
@@ -3553,7 +3598,7 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B63" t="s">
         <v>2</v>
@@ -3571,33 +3616,33 @@
         <v>11</v>
       </c>
       <c r="G63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H63" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I63" t="s">
         <v>16</v>
       </c>
       <c r="J63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L63" t="s">
         <v>22</v>
       </c>
       <c r="M63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>92</v>
+        <v>217</v>
       </c>
       <c r="B64" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" t="s">
         <v>3</v>
@@ -3612,19 +3657,19 @@
         <v>27</v>
       </c>
       <c r="G64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I64" t="s">
         <v>16</v>
       </c>
       <c r="J64" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L64" t="s">
         <v>23</v>
@@ -3635,7 +3680,7 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B65" t="s">
         <v>1</v>
@@ -3650,13 +3695,13 @@
         <v>9</v>
       </c>
       <c r="F65" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H65" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I65" t="s">
         <v>16</v>
@@ -3665,7 +3710,7 @@
         <v>16</v>
       </c>
       <c r="K65" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L65" t="s">
         <v>22</v>
@@ -3676,7 +3721,7 @@
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B66" t="s">
         <v>2</v>
@@ -3691,13 +3736,13 @@
         <v>9</v>
       </c>
       <c r="F66" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G66" t="s">
         <v>16</v>
       </c>
       <c r="H66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I66" t="s">
         <v>16</v>
@@ -3706,18 +3751,18 @@
         <v>16</v>
       </c>
       <c r="K66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M66" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B67" t="s">
         <v>1</v>
@@ -3726,31 +3771,31 @@
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F67" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G67" t="s">
         <v>16</v>
       </c>
       <c r="H67" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I67" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J67" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L67" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M67" t="s">
         <v>25</v>
@@ -3758,7 +3803,7 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>96</v>
+        <v>218</v>
       </c>
       <c r="B68" t="s">
         <v>1</v>
@@ -3767,39 +3812,39 @@
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E68" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F68" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G68" t="s">
         <v>16</v>
       </c>
       <c r="H68" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I68" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J68" t="s">
         <v>16</v>
       </c>
       <c r="K68" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L68" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>97</v>
+        <v>219</v>
       </c>
       <c r="B69" t="s">
         <v>1</v>
@@ -3823,10 +3868,10 @@
         <v>16</v>
       </c>
       <c r="I69" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K69" t="s">
         <v>20</v>
@@ -3835,12 +3880,12 @@
         <v>23</v>
       </c>
       <c r="M69" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B70" t="s">
         <v>1</v>
@@ -3864,27 +3909,27 @@
         <v>15</v>
       </c>
       <c r="I70" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J70" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K70" t="s">
         <v>21</v>
       </c>
       <c r="L70" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M70" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B71" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" t="s">
         <v>3</v>
@@ -3896,7 +3941,7 @@
         <v>9</v>
       </c>
       <c r="F71" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G71" t="s">
         <v>16</v>
@@ -3905,24 +3950,24 @@
         <v>16</v>
       </c>
       <c r="I71" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J71" t="s">
         <v>16</v>
       </c>
       <c r="K71" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L71" t="s">
         <v>23</v>
       </c>
       <c r="M71" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B72" t="s">
         <v>1</v>
@@ -3937,13 +3982,13 @@
         <v>9</v>
       </c>
       <c r="F72" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G72" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I72" t="s">
         <v>15</v>
@@ -3952,7 +3997,7 @@
         <v>16</v>
       </c>
       <c r="K72" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L72" t="s">
         <v>22</v>
@@ -3963,7 +4008,7 @@
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B73" t="s">
         <v>1</v>
@@ -3972,42 +4017,42 @@
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E73" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F73" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G73" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J73" t="s">
         <v>16</v>
       </c>
       <c r="K73" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L73" t="s">
         <v>22</v>
       </c>
       <c r="M73" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>102</v>
+        <v>220</v>
       </c>
       <c r="B74" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74" t="s">
         <v>3</v>
@@ -4019,33 +4064,33 @@
         <v>8</v>
       </c>
       <c r="F74" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G74" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H74" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I74" t="s">
         <v>15</v>
       </c>
       <c r="J74" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K74" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L74" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M74" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B75" t="s">
         <v>1</v>
@@ -4054,25 +4099,25 @@
         <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E75" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G75" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H75" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I75" t="s">
         <v>15</v>
       </c>
       <c r="J75" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K75" t="s">
         <v>20</v>
@@ -4086,7 +4131,7 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B76" t="s">
         <v>1</v>
@@ -4095,42 +4140,42 @@
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E76" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F76" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G76" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H76" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I76" t="s">
         <v>15</v>
       </c>
       <c r="J76" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K76" t="s">
         <v>21</v>
       </c>
       <c r="L76" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M76" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B77" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77" t="s">
         <v>3</v>
@@ -4142,7 +4187,7 @@
         <v>9</v>
       </c>
       <c r="F77" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G77" t="s">
         <v>16</v>
@@ -4151,42 +4196,42 @@
         <v>16</v>
       </c>
       <c r="I77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J77" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K77" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L77" t="s">
         <v>23</v>
       </c>
       <c r="M77" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B78" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78" t="s">
         <v>3</v>
       </c>
       <c r="D78" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E78" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F78" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G78" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H78" t="s">
         <v>16</v>
@@ -4198,10 +4243,10 @@
         <v>16</v>
       </c>
       <c r="K78" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L78" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M78" t="s">
         <v>25</v>
@@ -4209,10 +4254,10 @@
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B79" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" t="s">
         <v>3</v>
@@ -4224,7 +4269,7 @@
         <v>9</v>
       </c>
       <c r="F79" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G79" t="s">
         <v>15</v>
@@ -4239,10 +4284,10 @@
         <v>16</v>
       </c>
       <c r="K79" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L79" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M79" t="s">
         <v>25</v>
@@ -4250,22 +4295,22 @@
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B80" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80" t="s">
         <v>3</v>
       </c>
       <c r="D80" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E80" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F80" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G80" t="s">
         <v>15</v>
@@ -4274,16 +4319,16 @@
         <v>15</v>
       </c>
       <c r="I80" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J80" t="s">
         <v>15</v>
       </c>
       <c r="K80" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L80" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M80" t="s">
         <v>26</v>
@@ -4291,7 +4336,7 @@
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B81" t="s">
         <v>1</v>
@@ -4300,19 +4345,19 @@
         <v>3</v>
       </c>
       <c r="D81" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E81" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F81" t="s">
         <v>12</v>
       </c>
       <c r="G81" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H81" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I81" t="s">
         <v>15</v>
@@ -4327,24 +4372,24 @@
         <v>23</v>
       </c>
       <c r="M81" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B82" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82" t="s">
         <v>3</v>
       </c>
       <c r="D82" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E82" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F82" t="s">
         <v>11</v>
@@ -4353,13 +4398,13 @@
         <v>15</v>
       </c>
       <c r="H82" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I82" t="s">
         <v>15</v>
       </c>
       <c r="J82" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K82" t="s">
         <v>21</v>
@@ -4373,10 +4418,10 @@
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B83" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83" t="s">
         <v>3</v>
@@ -4391,16 +4436,16 @@
         <v>27</v>
       </c>
       <c r="G83" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H83" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I83" t="s">
         <v>16</v>
       </c>
       <c r="J83" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K83" t="s">
         <v>20</v>
@@ -4414,19 +4459,19 @@
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B84" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84" t="s">
         <v>3</v>
       </c>
       <c r="D84" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E84" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F84" t="s">
         <v>12</v>
@@ -4438,16 +4483,16 @@
         <v>16</v>
       </c>
       <c r="I84" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J84" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K84" t="s">
         <v>21</v>
       </c>
       <c r="L84" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M84" t="s">
         <v>25</v>
@@ -4455,10 +4500,10 @@
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B85" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85" t="s">
         <v>3</v>
@@ -4473,22 +4518,22 @@
         <v>11</v>
       </c>
       <c r="G85" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H85" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I85" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J85" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K85" t="s">
         <v>20</v>
       </c>
       <c r="L85" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M85" t="s">
         <v>25</v>
@@ -4496,7 +4541,7 @@
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B86" t="s">
         <v>1</v>
@@ -4505,10 +4550,10 @@
         <v>3</v>
       </c>
       <c r="D86" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E86" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F86" t="s">
         <v>27</v>
@@ -4532,12 +4577,12 @@
         <v>22</v>
       </c>
       <c r="M86" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B87" t="s">
         <v>1</v>
@@ -4546,10 +4591,10 @@
         <v>3</v>
       </c>
       <c r="D87" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E87" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F87" t="s">
         <v>12</v>
@@ -4561,7 +4606,7 @@
         <v>16</v>
       </c>
       <c r="I87" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J87" t="s">
         <v>15</v>
@@ -4573,12 +4618,12 @@
         <v>23</v>
       </c>
       <c r="M87" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B88" t="s">
         <v>2</v>
@@ -4599,7 +4644,7 @@
         <v>15</v>
       </c>
       <c r="H88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I88" t="s">
         <v>15</v>
@@ -4619,7 +4664,7 @@
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B89" t="s">
         <v>1</v>
@@ -4628,19 +4673,19 @@
         <v>3</v>
       </c>
       <c r="D89" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E89" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F89" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G89" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H89" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I89" t="s">
         <v>16</v>
@@ -4652,39 +4697,39 @@
         <v>20</v>
       </c>
       <c r="L89" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M89" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B90" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90" t="s">
         <v>3</v>
       </c>
       <c r="D90" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E90" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F90" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G90" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H90" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I90" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J90" t="s">
         <v>15</v>
@@ -4696,12 +4741,12 @@
         <v>22</v>
       </c>
       <c r="M90" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="B91" t="s">
         <v>1</v>
@@ -4710,16 +4755,16 @@
         <v>3</v>
       </c>
       <c r="D91" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E91" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F91" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G91" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -4734,15 +4779,15 @@
         <v>20</v>
       </c>
       <c r="L91" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M91" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B92" t="s">
         <v>1</v>
@@ -4751,25 +4796,25 @@
         <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E92" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F92" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G92" t="s">
         <v>15</v>
       </c>
       <c r="H92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I92" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K92" t="s">
         <v>21</v>
@@ -4778,53 +4823,53 @@
         <v>22</v>
       </c>
       <c r="M92" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="B93" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E93" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F93" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G93" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H93" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I93" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J93" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K93" t="s">
         <v>20</v>
       </c>
       <c r="L93" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M93" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B94" t="s">
         <v>2</v>
@@ -4839,19 +4884,19 @@
         <v>9</v>
       </c>
       <c r="F94" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G94" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H94" t="s">
         <v>16</v>
       </c>
       <c r="I94" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J94" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K94" t="s">
         <v>21</v>
@@ -4865,7 +4910,7 @@
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B95" t="s">
         <v>1</v>
@@ -4883,16 +4928,16 @@
         <v>11</v>
       </c>
       <c r="G95" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H95" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I95" t="s">
         <v>16</v>
       </c>
       <c r="J95" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K95" t="s">
         <v>20</v>
@@ -4906,37 +4951,37 @@
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B96" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96" t="s">
         <v>3</v>
       </c>
       <c r="D96" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E96" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F96" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G96" t="s">
         <v>15</v>
       </c>
       <c r="H96" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I96" t="s">
         <v>15</v>
       </c>
       <c r="J96" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K96" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L96" t="s">
         <v>22</v>
@@ -4947,7 +4992,7 @@
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B97" t="s">
         <v>1</v>
@@ -4962,25 +5007,25 @@
         <v>8</v>
       </c>
       <c r="F97" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G97" t="s">
         <v>15</v>
       </c>
       <c r="H97" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I97" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J97" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K97" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L97" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M97" t="s">
         <v>26</v>
@@ -4988,10 +5033,10 @@
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B98" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98" t="s">
         <v>3</v>
@@ -5003,25 +5048,25 @@
         <v>9</v>
       </c>
       <c r="F98" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G98" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H98" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I98" t="s">
         <v>15</v>
       </c>
       <c r="J98" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K98" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L98" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M98" t="s">
         <v>26</v>
@@ -5029,13 +5074,13 @@
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B99" t="s">
         <v>2</v>
       </c>
       <c r="C99" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D99" t="s">
         <v>8</v>
@@ -5044,13 +5089,13 @@
         <v>9</v>
       </c>
       <c r="F99" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G99" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H99" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I99" t="s">
         <v>15</v>
@@ -5070,22 +5115,22 @@
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B100" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100" t="s">
         <v>3</v>
       </c>
       <c r="D100" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E100" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F100" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G100" t="s">
         <v>16</v>
@@ -5103,15 +5148,15 @@
         <v>21</v>
       </c>
       <c r="L100" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M100" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B101" t="s">
         <v>1</v>
@@ -5120,10 +5165,10 @@
         <v>3</v>
       </c>
       <c r="D101" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E101" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F101" t="s">
         <v>11</v>
@@ -5135,16 +5180,16 @@
         <v>15</v>
       </c>
       <c r="I101" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J101" t="s">
         <v>15</v>
       </c>
       <c r="K101" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L101" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M101" t="s">
         <v>26</v>
@@ -5152,10 +5197,10 @@
     </row>
     <row r="102" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B102" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102" t="s">
         <v>3</v>
@@ -5167,7 +5212,7 @@
         <v>9</v>
       </c>
       <c r="F102" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G102" t="s">
         <v>15</v>
@@ -5176,7 +5221,7 @@
         <v>16</v>
       </c>
       <c r="I102" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J102" t="s">
         <v>16</v>
@@ -5185,18 +5230,18 @@
         <v>20</v>
       </c>
       <c r="L102" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M102" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B103" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103" t="s">
         <v>3</v>
@@ -5208,19 +5253,19 @@
         <v>8</v>
       </c>
       <c r="F103" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G103" t="s">
         <v>15</v>
       </c>
       <c r="H103" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I103" t="s">
         <v>16</v>
       </c>
       <c r="J103" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K103" t="s">
         <v>21</v>
@@ -5229,12 +5274,12 @@
         <v>22</v>
       </c>
       <c r="M103" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B104" t="s">
         <v>2</v>
@@ -5249,7 +5294,7 @@
         <v>9</v>
       </c>
       <c r="F104" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G104" t="s">
         <v>16</v>
@@ -5258,7 +5303,7 @@
         <v>15</v>
       </c>
       <c r="I104" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J104" t="s">
         <v>15</v>
@@ -5267,7 +5312,7 @@
         <v>20</v>
       </c>
       <c r="L104" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M104" t="s">
         <v>26</v>
@@ -5275,22 +5320,22 @@
     </row>
     <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B105" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105" t="s">
         <v>3</v>
       </c>
       <c r="D105" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E105" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F105" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G105" t="s">
         <v>16</v>
@@ -5316,7 +5361,7 @@
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B106" t="s">
         <v>1</v>
@@ -5334,36 +5379,36 @@
         <v>27</v>
       </c>
       <c r="G106" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H106" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I106" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J106" t="s">
         <v>16</v>
       </c>
       <c r="K106" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L106" t="s">
         <v>23</v>
       </c>
       <c r="M106" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B107" t="s">
         <v>1</v>
       </c>
       <c r="C107" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D107" t="s">
         <v>8</v>
@@ -5372,13 +5417,13 @@
         <v>9</v>
       </c>
       <c r="F107" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G107" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H107" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I107" t="s">
         <v>15</v>
@@ -5390,18 +5435,18 @@
         <v>21</v>
       </c>
       <c r="L107" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M107" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B108" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C108" t="s">
         <v>3</v>
@@ -5416,7 +5461,7 @@
         <v>27</v>
       </c>
       <c r="G108" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H108" t="s">
         <v>16</v>
@@ -5428,10 +5473,10 @@
         <v>16</v>
       </c>
       <c r="K108" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L108" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M108" t="s">
         <v>25</v>
@@ -5439,10 +5484,10 @@
     </row>
     <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B109" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C109" t="s">
         <v>3</v>
@@ -5463,13 +5508,13 @@
         <v>15</v>
       </c>
       <c r="I109" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J109" t="s">
         <v>15</v>
       </c>
       <c r="K109" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L109" t="s">
         <v>22</v>
@@ -5480,7 +5525,7 @@
     </row>
     <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B110" t="s">
         <v>2</v>
@@ -5498,51 +5543,51 @@
         <v>11</v>
       </c>
       <c r="G110" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H110" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I110" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J110" t="s">
         <v>15</v>
       </c>
       <c r="K110" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L110" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M110" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>139</v>
+        <v>221</v>
       </c>
       <c r="B111" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111" t="s">
         <v>3</v>
       </c>
       <c r="D111" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E111" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F111" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G111" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H111" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I111" t="s">
         <v>15</v>
@@ -5557,15 +5602,15 @@
         <v>22</v>
       </c>
       <c r="M111" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B112" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112" t="s">
         <v>3</v>
@@ -5577,7 +5622,7 @@
         <v>8</v>
       </c>
       <c r="F112" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G112" t="s">
         <v>16</v>
@@ -5586,7 +5631,7 @@
         <v>16</v>
       </c>
       <c r="I112" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J112" t="s">
         <v>16</v>
@@ -5603,10 +5648,10 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B113" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C113" t="s">
         <v>3</v>
@@ -5621,7 +5666,7 @@
         <v>27</v>
       </c>
       <c r="G113" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H113" t="s">
         <v>15</v>
@@ -5630,13 +5675,13 @@
         <v>15</v>
       </c>
       <c r="J113" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K113" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L113" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M113" t="s">
         <v>26</v>
@@ -5644,13 +5689,13 @@
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="B114" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D114" t="s">
         <v>8</v>
@@ -5662,7 +5707,7 @@
         <v>12</v>
       </c>
       <c r="G114" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H114" t="s">
         <v>16</v>
@@ -5671,10 +5716,10 @@
         <v>15</v>
       </c>
       <c r="J114" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K114" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L114" t="s">
         <v>22</v>
@@ -5685,10 +5730,10 @@
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B115" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C115" t="s">
         <v>3</v>
@@ -5712,33 +5757,33 @@
         <v>16</v>
       </c>
       <c r="J115" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K115" t="s">
         <v>21</v>
       </c>
       <c r="L115" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M115" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B116" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C116" t="s">
         <v>3</v>
       </c>
       <c r="D116" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E116" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F116" t="s">
         <v>12</v>
@@ -5747,19 +5792,19 @@
         <v>15</v>
       </c>
       <c r="H116" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I116" t="s">
         <v>15</v>
       </c>
       <c r="J116" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K116" t="s">
         <v>20</v>
       </c>
       <c r="L116" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M116" t="s">
         <v>25</v>
@@ -5767,7 +5812,7 @@
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B117" t="s">
         <v>2</v>
@@ -5785,7 +5830,7 @@
         <v>11</v>
       </c>
       <c r="G117" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H117" t="s">
         <v>16</v>
@@ -5794,7 +5839,7 @@
         <v>15</v>
       </c>
       <c r="J117" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K117" t="s">
         <v>21</v>
@@ -5808,89 +5853,89 @@
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B118" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C118" t="s">
         <v>3</v>
       </c>
       <c r="D118" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E118" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F118" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G118" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H118" t="s">
         <v>15</v>
       </c>
       <c r="I118" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J118" t="s">
         <v>15</v>
       </c>
       <c r="K118" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L118" t="s">
         <v>22</v>
       </c>
       <c r="M118" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B119" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119" t="s">
         <v>3</v>
       </c>
       <c r="D119" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E119" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F119" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G119" t="s">
         <v>16</v>
       </c>
       <c r="H119" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I119" t="s">
         <v>16</v>
       </c>
       <c r="J119" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K119" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L119" t="s">
         <v>22</v>
       </c>
       <c r="M119" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B120" t="s">
         <v>2</v>
@@ -5905,22 +5950,22 @@
         <v>8</v>
       </c>
       <c r="F120" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G120" t="s">
         <v>16</v>
       </c>
       <c r="H120" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I120" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J120" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K120" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L120" t="s">
         <v>22</v>
@@ -5931,7 +5976,7 @@
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="B121" t="s">
         <v>2</v>
@@ -5940,22 +5985,22 @@
         <v>3</v>
       </c>
       <c r="D121" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E121" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F121" t="s">
         <v>12</v>
       </c>
       <c r="G121" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H121" t="s">
         <v>16</v>
       </c>
       <c r="I121" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J121" t="s">
         <v>16</v>
@@ -5964,7 +6009,7 @@
         <v>20</v>
       </c>
       <c r="L121" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M121" t="s">
         <v>25</v>
@@ -5972,25 +6017,25 @@
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>150</v>
+        <v>222</v>
       </c>
       <c r="B122" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122" t="s">
         <v>3</v>
       </c>
       <c r="D122" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E122" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F122" t="s">
         <v>11</v>
       </c>
       <c r="G122" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H122" t="s">
         <v>15</v>
@@ -6005,15 +6050,15 @@
         <v>21</v>
       </c>
       <c r="L122" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M122" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>151</v>
+        <v>223</v>
       </c>
       <c r="B123" t="s">
         <v>2</v>
@@ -6022,10 +6067,10 @@
         <v>3</v>
       </c>
       <c r="D123" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F123" t="s">
         <v>27</v>
@@ -6037,10 +6082,10 @@
         <v>15</v>
       </c>
       <c r="I123" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J123" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K123" t="s">
         <v>20</v>
@@ -6049,15 +6094,15 @@
         <v>23</v>
       </c>
       <c r="M123" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>152</v>
+        <v>224</v>
       </c>
       <c r="B124" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C124" t="s">
         <v>3</v>
@@ -6069,13 +6114,13 @@
         <v>8</v>
       </c>
       <c r="F124" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G124" t="s">
         <v>16</v>
       </c>
       <c r="H124" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I124" t="s">
         <v>16</v>
@@ -6084,7 +6129,7 @@
         <v>16</v>
       </c>
       <c r="K124" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L124" t="s">
         <v>23</v>
@@ -6095,7 +6140,7 @@
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B125" t="s">
         <v>2</v>
@@ -6110,13 +6155,13 @@
         <v>9</v>
       </c>
       <c r="F125" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G125" t="s">
         <v>16</v>
       </c>
       <c r="H125" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I125" t="s">
         <v>16</v>
@@ -6125,10 +6170,10 @@
         <v>15</v>
       </c>
       <c r="K125" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L125" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M125" t="s">
         <v>26</v>
@@ -6136,7 +6181,7 @@
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B126" t="s">
         <v>2</v>
@@ -6145,31 +6190,31 @@
         <v>3</v>
       </c>
       <c r="D126" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E126" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F126" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G126" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H126" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I126" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J126" t="s">
         <v>16</v>
       </c>
       <c r="K126" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L126" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M126" t="s">
         <v>25</v>
@@ -6177,7 +6222,7 @@
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="B127" t="s">
         <v>2</v>
@@ -6186,25 +6231,25 @@
         <v>3</v>
       </c>
       <c r="D127" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E127" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F127" t="s">
         <v>11</v>
       </c>
       <c r="G127" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H127" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I127" t="s">
         <v>15</v>
       </c>
       <c r="J127" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K127" t="s">
         <v>21</v>
@@ -6213,15 +6258,15 @@
         <v>23</v>
       </c>
       <c r="M127" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="B128" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128" t="s">
         <v>3</v>
@@ -6251,7 +6296,7 @@
         <v>20</v>
       </c>
       <c r="L128" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M128" t="s">
         <v>26</v>
@@ -6259,10 +6304,10 @@
     </row>
     <row r="129" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B129" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C129" t="s">
         <v>3</v>
@@ -6277,7 +6322,7 @@
         <v>12</v>
       </c>
       <c r="G129" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H129" t="s">
         <v>15</v>
@@ -6292,7 +6337,7 @@
         <v>21</v>
       </c>
       <c r="L129" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M129" t="s">
         <v>26</v>
@@ -6300,10 +6345,10 @@
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B130" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C130" t="s">
         <v>3</v>
@@ -6333,7 +6378,7 @@
         <v>20</v>
       </c>
       <c r="L130" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M130" t="s">
         <v>26</v>
@@ -6341,10 +6386,10 @@
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B131" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C131" t="s">
         <v>3</v>
@@ -6356,25 +6401,25 @@
         <v>8</v>
       </c>
       <c r="F131" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G131" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H131" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I131" t="s">
         <v>16</v>
       </c>
       <c r="J131" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K131" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L131" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M131" t="s">
         <v>25</v>
@@ -6382,10 +6427,10 @@
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="B132" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C132" t="s">
         <v>3</v>
@@ -6397,33 +6442,33 @@
         <v>8</v>
       </c>
       <c r="F132" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G132" t="s">
         <v>15</v>
       </c>
       <c r="H132" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I132" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J132" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K132" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L132" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M132" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="B133" t="s">
         <v>2</v>
@@ -6432,13 +6477,13 @@
         <v>3</v>
       </c>
       <c r="D133" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E133" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F133" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G133" t="s">
         <v>15</v>
@@ -6447,13 +6492,13 @@
         <v>15</v>
       </c>
       <c r="I133" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J133" t="s">
         <v>15</v>
       </c>
       <c r="K133" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L133" t="s">
         <v>23</v>
@@ -6464,34 +6509,34 @@
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="B134" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C134" t="s">
         <v>3</v>
       </c>
       <c r="D134" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E134" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F134" t="s">
         <v>12</v>
       </c>
       <c r="G134" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H134" t="s">
         <v>15</v>
       </c>
       <c r="I134" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J134" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K134" t="s">
         <v>21</v>
@@ -6500,15 +6545,15 @@
         <v>23</v>
       </c>
       <c r="M134" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B135" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C135" t="s">
         <v>3</v>
@@ -6523,7 +6568,7 @@
         <v>11</v>
       </c>
       <c r="G135" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H135" t="s">
         <v>15</v>
@@ -6538,45 +6583,45 @@
         <v>20</v>
       </c>
       <c r="L135" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M135" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="B136" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C136" t="s">
         <v>3</v>
       </c>
       <c r="D136" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E136" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F136" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G136" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H136" t="s">
         <v>15</v>
       </c>
       <c r="I136" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J136" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K136" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L136" t="s">
         <v>22</v>
@@ -6587,7 +6632,7 @@
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>165</v>
+        <v>225</v>
       </c>
       <c r="B137" t="s">
         <v>2</v>
@@ -6602,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="F137" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G137" t="s">
         <v>16</v>
@@ -6611,13 +6656,13 @@
         <v>15</v>
       </c>
       <c r="I137" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J137" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K137" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L137" t="s">
         <v>22</v>
@@ -6628,10 +6673,10 @@
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="B138" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C138" t="s">
         <v>3</v>
@@ -6643,7 +6688,7 @@
         <v>8</v>
       </c>
       <c r="F138" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G138" t="s">
         <v>15</v>
@@ -6652,13 +6697,13 @@
         <v>15</v>
       </c>
       <c r="I138" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J138" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K138" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L138" t="s">
         <v>23</v>
@@ -6669,7 +6714,7 @@
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="B139" t="s">
         <v>1</v>
@@ -6684,10 +6729,10 @@
         <v>9</v>
       </c>
       <c r="F139" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G139" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H139" t="s">
         <v>15</v>
@@ -6699,18 +6744,18 @@
         <v>15</v>
       </c>
       <c r="K139" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L139" t="s">
         <v>23</v>
       </c>
       <c r="M139" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="B140" t="s">
         <v>2</v>
@@ -6719,19 +6764,19 @@
         <v>3</v>
       </c>
       <c r="D140" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E140" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F140" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G140" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H140" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I140" t="s">
         <v>16</v>
@@ -6740,7 +6785,7 @@
         <v>15</v>
       </c>
       <c r="K140" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L140" t="s">
         <v>23</v>
@@ -6751,37 +6796,37 @@
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="B141" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C141" t="s">
         <v>3</v>
       </c>
       <c r="D141" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E141" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F141" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G141" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H141" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I141" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J141" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K141" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L141" t="s">
         <v>23</v>
@@ -6792,34 +6837,34 @@
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B142" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C142" t="s">
         <v>3</v>
       </c>
       <c r="D142" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E142" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F142" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G142" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H142" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I142" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J142" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K142" t="s">
         <v>21</v>
@@ -6833,7 +6878,7 @@
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="B143" t="s">
         <v>2</v>
@@ -6842,28 +6887,28 @@
         <v>3</v>
       </c>
       <c r="D143" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E143" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F143" t="s">
         <v>12</v>
       </c>
       <c r="G143" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H143" t="s">
         <v>16</v>
       </c>
       <c r="I143" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J143" t="s">
         <v>16</v>
       </c>
       <c r="K143" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L143" t="s">
         <v>22</v>
@@ -6874,10 +6919,10 @@
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="B144" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C144" t="s">
         <v>3</v>
@@ -6895,7 +6940,7 @@
         <v>15</v>
       </c>
       <c r="H144" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I144" t="s">
         <v>15</v>
@@ -6904,18 +6949,18 @@
         <v>15</v>
       </c>
       <c r="K144" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L144" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M144" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="145" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="B145" t="s">
         <v>1</v>
@@ -6930,13 +6975,13 @@
         <v>9</v>
       </c>
       <c r="F145" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G145" t="s">
         <v>15</v>
       </c>
       <c r="H145" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I145" t="s">
         <v>15</v>
@@ -6948,7 +6993,7 @@
         <v>21</v>
       </c>
       <c r="L145" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M145" t="s">
         <v>26</v>
@@ -6956,10 +7001,10 @@
     </row>
     <row r="146" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="B146" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C146" t="s">
         <v>3</v>
@@ -6971,19 +7016,19 @@
         <v>9</v>
       </c>
       <c r="F146" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G146" t="s">
         <v>15</v>
       </c>
       <c r="H146" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I146" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J146" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K146" t="s">
         <v>20</v>
@@ -6997,10 +7042,10 @@
     </row>
     <row r="147" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B147" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C147" t="s">
         <v>3</v>
@@ -7012,25 +7057,25 @@
         <v>9</v>
       </c>
       <c r="F147" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G147" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H147" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I147" t="s">
         <v>15</v>
       </c>
       <c r="J147" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K147" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L147" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M147" t="s">
         <v>25</v>
@@ -7038,10 +7083,10 @@
     </row>
     <row r="148" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="B148" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C148" t="s">
         <v>3</v>
@@ -7053,22 +7098,22 @@
         <v>8</v>
       </c>
       <c r="F148" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G148" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H148" t="s">
         <v>15</v>
       </c>
       <c r="I148" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J148" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K148" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L148" t="s">
         <v>22</v>
@@ -7079,40 +7124,40 @@
     </row>
     <row r="149" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B149" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C149" t="s">
         <v>3</v>
       </c>
       <c r="D149" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E149" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F149" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G149" t="s">
         <v>15</v>
       </c>
       <c r="H149" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I149" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J149" t="s">
         <v>16</v>
       </c>
       <c r="K149" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L149" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M149" t="s">
         <v>26</v>
@@ -7120,7 +7165,7 @@
     </row>
     <row r="150" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="B150" t="s">
         <v>1</v>
@@ -7129,16 +7174,16 @@
         <v>3</v>
       </c>
       <c r="D150" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E150" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F150" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G150" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H150" t="s">
         <v>15</v>
@@ -7150,18 +7195,18 @@
         <v>15</v>
       </c>
       <c r="K150" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L150" t="s">
         <v>23</v>
       </c>
       <c r="M150" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B151" t="s">
         <v>2</v>
@@ -7170,13 +7215,13 @@
         <v>3</v>
       </c>
       <c r="D151" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E151" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F151" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G151" t="s">
         <v>16</v>
@@ -7185,27 +7230,27 @@
         <v>16</v>
       </c>
       <c r="I151" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J151" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K151" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L151" t="s">
         <v>23</v>
       </c>
       <c r="M151" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="152" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B152" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C152" t="s">
         <v>3</v>
@@ -7217,25 +7262,25 @@
         <v>9</v>
       </c>
       <c r="F152" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G152" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H152" t="s">
         <v>15</v>
       </c>
       <c r="I152" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J152" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K152" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L152" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M152" t="s">
         <v>26</v>
@@ -7243,10 +7288,10 @@
     </row>
     <row r="153" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="B153" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C153" t="s">
         <v>3</v>
@@ -7267,27 +7312,27 @@
         <v>16</v>
       </c>
       <c r="I153" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J153" t="s">
         <v>16</v>
       </c>
       <c r="K153" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L153" t="s">
         <v>22</v>
       </c>
       <c r="M153" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="B154" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C154" t="s">
         <v>3</v>
@@ -7308,39 +7353,39 @@
         <v>16</v>
       </c>
       <c r="I154" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J154" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K154" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L154" t="s">
         <v>22</v>
       </c>
       <c r="M154" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>183</v>
+        <v>227</v>
       </c>
       <c r="B155" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C155" t="s">
         <v>3</v>
       </c>
       <c r="D155" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E155" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F155" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G155" t="s">
         <v>15</v>
@@ -7352,13 +7397,13 @@
         <v>16</v>
       </c>
       <c r="J155" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K155" t="s">
         <v>20</v>
       </c>
       <c r="L155" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M155" t="s">
         <v>25</v>
@@ -7366,10 +7411,10 @@
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="B156" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C156" t="s">
         <v>3</v>
@@ -7381,19 +7426,19 @@
         <v>9</v>
       </c>
       <c r="F156" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G156" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H156" t="s">
         <v>16</v>
       </c>
       <c r="I156" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J156" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K156" t="s">
         <v>21</v>
@@ -7402,56 +7447,56 @@
         <v>22</v>
       </c>
       <c r="M156" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="B157" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C157" t="s">
         <v>3</v>
       </c>
       <c r="D157" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E157" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F157" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G157" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H157" t="s">
         <v>16</v>
       </c>
       <c r="I157" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J157" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K157" t="s">
         <v>20</v>
       </c>
       <c r="L157" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M157" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="B158" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C158" t="s">
         <v>3</v>
@@ -7463,22 +7508,22 @@
         <v>9</v>
       </c>
       <c r="F158" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G158" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H158" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I158" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J158" t="s">
         <v>15</v>
       </c>
       <c r="K158" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L158" t="s">
         <v>22</v>
@@ -7489,7 +7534,7 @@
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="B159" t="s">
         <v>2</v>
@@ -7504,33 +7549,33 @@
         <v>9</v>
       </c>
       <c r="F159" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G159" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H159" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I159" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J159" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K159" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L159" t="s">
         <v>23</v>
       </c>
       <c r="M159" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="B160" t="s">
         <v>2</v>
@@ -7545,7 +7590,7 @@
         <v>9</v>
       </c>
       <c r="F160" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G160" t="s">
         <v>16</v>
@@ -7554,16 +7599,16 @@
         <v>16</v>
       </c>
       <c r="I160" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J160" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K160" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L160" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M160" t="s">
         <v>25</v>
@@ -7571,63 +7616,63 @@
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="B161" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C161" t="s">
         <v>3</v>
       </c>
       <c r="D161" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E161" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F161" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G161" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H161" t="s">
         <v>15</v>
       </c>
       <c r="I161" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J161" t="s">
         <v>16</v>
       </c>
       <c r="K161" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L161" t="s">
         <v>22</v>
       </c>
       <c r="M161" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="162" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="B162" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C162" t="s">
         <v>3</v>
       </c>
       <c r="D162" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E162" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F162" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G162" t="s">
         <v>15</v>
@@ -7636,24 +7681,24 @@
         <v>16</v>
       </c>
       <c r="I162" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J162" t="s">
         <v>16</v>
       </c>
       <c r="K162" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L162" t="s">
         <v>22</v>
       </c>
       <c r="M162" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="163" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="B163" t="s">
         <v>1</v>
@@ -7662,28 +7707,28 @@
         <v>3</v>
       </c>
       <c r="D163" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E163" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F163" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G163" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H163" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I163" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J163" t="s">
         <v>15</v>
       </c>
       <c r="K163" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L163" t="s">
         <v>23</v>
@@ -7694,51 +7739,51 @@
     </row>
     <row r="164" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="B164" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C164" t="s">
         <v>3</v>
       </c>
       <c r="D164" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E164" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F164" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G164" t="s">
         <v>16</v>
       </c>
       <c r="H164" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I164" t="s">
         <v>15</v>
       </c>
       <c r="J164" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K164" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L164" t="s">
         <v>23</v>
       </c>
       <c r="M164" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="165" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="B165" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C165" t="s">
         <v>3</v>
@@ -7762,7 +7807,7 @@
         <v>16</v>
       </c>
       <c r="J165" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K165" t="s">
         <v>20</v>
@@ -7771,12 +7816,12 @@
         <v>22</v>
       </c>
       <c r="M165" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="166" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="B166" t="s">
         <v>1</v>
@@ -7785,13 +7830,13 @@
         <v>3</v>
       </c>
       <c r="D166" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E166" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F166" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G166" t="s">
         <v>15</v>
@@ -7809,7 +7854,7 @@
         <v>21</v>
       </c>
       <c r="L166" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M166" t="s">
         <v>26</v>
@@ -7817,7 +7862,7 @@
     </row>
     <row r="167" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="B167" t="s">
         <v>1</v>
@@ -7832,25 +7877,25 @@
         <v>9</v>
       </c>
       <c r="F167" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G167" t="s">
         <v>16</v>
       </c>
       <c r="H167" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I167" t="s">
         <v>16</v>
       </c>
       <c r="J167" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K167" t="s">
         <v>20</v>
       </c>
       <c r="L167" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M167" t="s">
         <v>26</v>
@@ -7858,7 +7903,7 @@
     </row>
     <row r="168" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="B168" t="s">
         <v>1</v>
@@ -7876,7 +7921,7 @@
         <v>12</v>
       </c>
       <c r="G168" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H168" t="s">
         <v>15</v>
@@ -7888,18 +7933,18 @@
         <v>16</v>
       </c>
       <c r="K168" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L168" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M168" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="169" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="B169" t="s">
         <v>1</v>
@@ -7908,63 +7953,63 @@
         <v>3</v>
       </c>
       <c r="D169" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E169" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F169" t="s">
         <v>11</v>
       </c>
       <c r="G169" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H169" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I169" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J169" t="s">
         <v>15</v>
       </c>
       <c r="K169" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L169" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M169" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="170" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="B170" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C170" t="s">
         <v>3</v>
       </c>
       <c r="D170" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E170" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F170" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G170" t="s">
         <v>16</v>
       </c>
       <c r="H170" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I170" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J170" t="s">
         <v>16</v>
@@ -7973,15 +8018,15 @@
         <v>20</v>
       </c>
       <c r="L170" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M170" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="171" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="B171" t="s">
         <v>2</v>
@@ -8002,19 +8047,19 @@
         <v>16</v>
       </c>
       <c r="H171" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I171" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J171" t="s">
         <v>15</v>
       </c>
       <c r="K171" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L171" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M171" t="s">
         <v>26</v>
@@ -8022,7 +8067,7 @@
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="B172" t="s">
         <v>2</v>
@@ -8031,19 +8076,19 @@
         <v>3</v>
       </c>
       <c r="D172" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E172" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F172" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G172" t="s">
         <v>16</v>
       </c>
       <c r="H172" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I172" t="s">
         <v>16</v>
@@ -8058,12 +8103,12 @@
         <v>23</v>
       </c>
       <c r="M172" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="B173" t="s">
         <v>2</v>
@@ -8072,19 +8117,19 @@
         <v>3</v>
       </c>
       <c r="D173" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E173" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F173" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G173" t="s">
         <v>16</v>
       </c>
       <c r="H173" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I173" t="s">
         <v>16</v>
@@ -8104,7 +8149,7 @@
     </row>
     <row r="174" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="B174" t="s">
         <v>2</v>
@@ -8113,19 +8158,19 @@
         <v>3</v>
       </c>
       <c r="D174" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E174" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F174" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G174" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H174" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I174" t="s">
         <v>16</v>
@@ -8134,18 +8179,18 @@
         <v>16</v>
       </c>
       <c r="K174" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L174" t="s">
         <v>22</v>
       </c>
       <c r="M174" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="B175" t="s">
         <v>1</v>
@@ -8154,16 +8199,16 @@
         <v>3</v>
       </c>
       <c r="D175" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E175" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F175" t="s">
         <v>27</v>
       </c>
       <c r="G175" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H175" t="s">
         <v>16</v>
@@ -8172,13 +8217,13 @@
         <v>16</v>
       </c>
       <c r="J175" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K175" t="s">
         <v>20</v>
       </c>
       <c r="L175" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M175" t="s">
         <v>25</v>
@@ -8186,48 +8231,48 @@
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="B176" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C176" t="s">
         <v>3</v>
       </c>
       <c r="D176" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E176" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F176" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G176" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H176" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I176" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J176" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K176" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L176" t="s">
         <v>23</v>
       </c>
       <c r="M176" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="B177" t="s">
         <v>1</v>
@@ -8236,13 +8281,13 @@
         <v>3</v>
       </c>
       <c r="D177" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E177" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F177" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G177" t="s">
         <v>16</v>
@@ -8251,27 +8296,27 @@
         <v>15</v>
       </c>
       <c r="I177" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J177" t="s">
         <v>15</v>
       </c>
       <c r="K177" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L177" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M177" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="178" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="B178" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C178" t="s">
         <v>3</v>
@@ -8283,19 +8328,19 @@
         <v>9</v>
       </c>
       <c r="F178" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G178" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H178" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I178" t="s">
         <v>16</v>
       </c>
       <c r="J178" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K178" t="s">
         <v>20</v>
@@ -8309,7 +8354,7 @@
     </row>
     <row r="179" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="B179" t="s">
         <v>1</v>
@@ -8318,16 +8363,16 @@
         <v>3</v>
       </c>
       <c r="D179" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E179" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F179" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G179" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H179" t="s">
         <v>16</v>
@@ -8342,7 +8387,7 @@
         <v>21</v>
       </c>
       <c r="L179" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M179" t="s">
         <v>26</v>
@@ -8350,7 +8395,7 @@
     </row>
     <row r="180" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="B180" t="s">
         <v>1</v>
@@ -8365,16 +8410,16 @@
         <v>9</v>
       </c>
       <c r="F180" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G180" t="s">
         <v>16</v>
       </c>
       <c r="H180" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I180" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J180" t="s">
         <v>16</v>
@@ -8383,7 +8428,7 @@
         <v>20</v>
       </c>
       <c r="L180" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M180" t="s">
         <v>26</v>
@@ -8391,10 +8436,10 @@
     </row>
     <row r="181" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>209</v>
+        <v>196</v>
       </c>
       <c r="B181" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C181" t="s">
         <v>3</v>
@@ -8406,19 +8451,19 @@
         <v>9</v>
       </c>
       <c r="F181" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="G181" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H181" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I181" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J181" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K181" t="s">
         <v>21</v>
@@ -8427,12 +8472,12 @@
         <v>23</v>
       </c>
       <c r="M181" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="182" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="B182" t="s">
         <v>1</v>
@@ -8441,22 +8486,22 @@
         <v>3</v>
       </c>
       <c r="D182" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E182" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F182" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G182" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H182" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I182" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J182" t="s">
         <v>15</v>
@@ -8465,7 +8510,7 @@
         <v>20</v>
       </c>
       <c r="L182" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M182" t="s">
         <v>26</v>
@@ -8473,7 +8518,7 @@
     </row>
     <row r="183" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="B183" t="s">
         <v>1</v>
@@ -8482,28 +8527,28 @@
         <v>3</v>
       </c>
       <c r="D183" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E183" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F183" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G183" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H183" t="s">
         <v>15</v>
       </c>
       <c r="I183" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J183" t="s">
         <v>16</v>
       </c>
       <c r="K183" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L183" t="s">
         <v>22</v>
@@ -8514,10 +8559,10 @@
     </row>
     <row r="184" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="B184" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C184" t="s">
         <v>3</v>
@@ -8529,10 +8574,10 @@
         <v>9</v>
       </c>
       <c r="F184" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G184" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H184" t="s">
         <v>16</v>
@@ -8544,21 +8589,21 @@
         <v>15</v>
       </c>
       <c r="K184" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L184" t="s">
         <v>23</v>
       </c>
       <c r="M184" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="185" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="B185" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C185" t="s">
         <v>3</v>
@@ -8573,65 +8618,680 @@
         <v>12</v>
       </c>
       <c r="G185" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H185" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I185" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J185" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K185" t="s">
         <v>21</v>
       </c>
       <c r="L185" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M185" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="186" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="B186" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C186" t="s">
         <v>3</v>
       </c>
       <c r="D186" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E186" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F186" t="s">
         <v>11</v>
       </c>
       <c r="G186" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H186" t="s">
         <v>15</v>
       </c>
       <c r="I186" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J186" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K186" t="s">
         <v>20</v>
       </c>
       <c r="L186" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M186" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>202</v>
+      </c>
+      <c r="B187" t="s">
+        <v>2</v>
+      </c>
+      <c r="C187" t="s">
+        <v>3</v>
+      </c>
+      <c r="D187" t="s">
+        <v>9</v>
+      </c>
+      <c r="E187" t="s">
+        <v>8</v>
+      </c>
+      <c r="F187" t="s">
+        <v>12</v>
+      </c>
+      <c r="G187" t="s">
+        <v>15</v>
+      </c>
+      <c r="H187" t="s">
+        <v>16</v>
+      </c>
+      <c r="I187" t="s">
+        <v>16</v>
+      </c>
+      <c r="J187" t="s">
+        <v>16</v>
+      </c>
+      <c r="K187" t="s">
+        <v>20</v>
+      </c>
+      <c r="L187" t="s">
+        <v>22</v>
+      </c>
+      <c r="M187" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>228</v>
+      </c>
+      <c r="B188" t="s">
+        <v>2</v>
+      </c>
+      <c r="C188" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" t="s">
+        <v>8</v>
+      </c>
+      <c r="E188" t="s">
+        <v>9</v>
+      </c>
+      <c r="F188" t="s">
+        <v>11</v>
+      </c>
+      <c r="G188" t="s">
+        <v>16</v>
+      </c>
+      <c r="H188" t="s">
+        <v>15</v>
+      </c>
+      <c r="I188" t="s">
+        <v>15</v>
+      </c>
+      <c r="J188" t="s">
+        <v>15</v>
+      </c>
+      <c r="K188" t="s">
+        <v>21</v>
+      </c>
+      <c r="L188" t="s">
+        <v>22</v>
+      </c>
+      <c r="M188" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>203</v>
+      </c>
+      <c r="B189" t="s">
+        <v>1</v>
+      </c>
+      <c r="C189" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" t="s">
+        <v>8</v>
+      </c>
+      <c r="E189" t="s">
+        <v>9</v>
+      </c>
+      <c r="F189" t="s">
+        <v>27</v>
+      </c>
+      <c r="G189" t="s">
+        <v>16</v>
+      </c>
+      <c r="H189" t="s">
+        <v>16</v>
+      </c>
+      <c r="I189" t="s">
+        <v>16</v>
+      </c>
+      <c r="J189" t="s">
+        <v>15</v>
+      </c>
+      <c r="K189" t="s">
+        <v>20</v>
+      </c>
+      <c r="L189" t="s">
+        <v>23</v>
+      </c>
+      <c r="M189" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>204</v>
+      </c>
+      <c r="B190" t="s">
+        <v>2</v>
+      </c>
+      <c r="C190" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" t="s">
+        <v>8</v>
+      </c>
+      <c r="F190" t="s">
+        <v>11</v>
+      </c>
+      <c r="G190" t="s">
+        <v>16</v>
+      </c>
+      <c r="H190" t="s">
+        <v>15</v>
+      </c>
+      <c r="I190" t="s">
+        <v>16</v>
+      </c>
+      <c r="J190" t="s">
+        <v>16</v>
+      </c>
+      <c r="K190" t="s">
+        <v>20</v>
+      </c>
+      <c r="L190" t="s">
+        <v>23</v>
+      </c>
+      <c r="M190" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>205</v>
+      </c>
+      <c r="B191" t="s">
+        <v>1</v>
+      </c>
+      <c r="C191" t="s">
+        <v>3</v>
+      </c>
+      <c r="D191" t="s">
+        <v>8</v>
+      </c>
+      <c r="E191" t="s">
+        <v>9</v>
+      </c>
+      <c r="F191" t="s">
+        <v>27</v>
+      </c>
+      <c r="G191" t="s">
+        <v>16</v>
+      </c>
+      <c r="H191" t="s">
+        <v>15</v>
+      </c>
+      <c r="I191" t="s">
+        <v>16</v>
+      </c>
+      <c r="J191" t="s">
+        <v>15</v>
+      </c>
+      <c r="K191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L191" t="s">
+        <v>22</v>
+      </c>
+      <c r="M191" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>229</v>
+      </c>
+      <c r="B192" t="s">
+        <v>2</v>
+      </c>
+      <c r="C192" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" t="s">
+        <v>8</v>
+      </c>
+      <c r="E192" t="s">
+        <v>9</v>
+      </c>
+      <c r="F192" t="s">
+        <v>12</v>
+      </c>
+      <c r="G192" t="s">
+        <v>15</v>
+      </c>
+      <c r="H192" t="s">
+        <v>15</v>
+      </c>
+      <c r="I192" t="s">
+        <v>16</v>
+      </c>
+      <c r="J192" t="s">
+        <v>15</v>
+      </c>
+      <c r="K192" t="s">
+        <v>20</v>
+      </c>
+      <c r="L192" t="s">
+        <v>22</v>
+      </c>
+      <c r="M192" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>206</v>
+      </c>
+      <c r="B193" t="s">
+        <v>1</v>
+      </c>
+      <c r="C193" t="s">
+        <v>3</v>
+      </c>
+      <c r="D193" t="s">
+        <v>8</v>
+      </c>
+      <c r="E193" t="s">
+        <v>9</v>
+      </c>
+      <c r="F193" t="s">
+        <v>27</v>
+      </c>
+      <c r="G193" t="s">
+        <v>15</v>
+      </c>
+      <c r="H193" t="s">
+        <v>16</v>
+      </c>
+      <c r="I193" t="s">
+        <v>16</v>
+      </c>
+      <c r="J193" t="s">
+        <v>16</v>
+      </c>
+      <c r="K193" t="s">
+        <v>20</v>
+      </c>
+      <c r="L193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M193" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>207</v>
+      </c>
+      <c r="B194" t="s">
+        <v>1</v>
+      </c>
+      <c r="C194" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" t="s">
+        <v>9</v>
+      </c>
+      <c r="E194" t="s">
+        <v>8</v>
+      </c>
+      <c r="F194" t="s">
+        <v>12</v>
+      </c>
+      <c r="G194" t="s">
+        <v>16</v>
+      </c>
+      <c r="H194" t="s">
+        <v>16</v>
+      </c>
+      <c r="I194" t="s">
+        <v>15</v>
+      </c>
+      <c r="J194" t="s">
+        <v>16</v>
+      </c>
+      <c r="K194" t="s">
+        <v>21</v>
+      </c>
+      <c r="L194" t="s">
+        <v>22</v>
+      </c>
+      <c r="M194" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>208</v>
+      </c>
+      <c r="B195" t="s">
+        <v>1</v>
+      </c>
+      <c r="C195" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" t="s">
+        <v>8</v>
+      </c>
+      <c r="E195" t="s">
+        <v>9</v>
+      </c>
+      <c r="F195" t="s">
+        <v>11</v>
+      </c>
+      <c r="G195" t="s">
+        <v>16</v>
+      </c>
+      <c r="H195" t="s">
+        <v>16</v>
+      </c>
+      <c r="I195" t="s">
+        <v>15</v>
+      </c>
+      <c r="J195" t="s">
+        <v>16</v>
+      </c>
+      <c r="K195" t="s">
+        <v>20</v>
+      </c>
+      <c r="L195" t="s">
+        <v>22</v>
+      </c>
+      <c r="M195" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>209</v>
+      </c>
+      <c r="B196" t="s">
+        <v>2</v>
+      </c>
+      <c r="C196" t="s">
+        <v>3</v>
+      </c>
+      <c r="D196" t="s">
+        <v>8</v>
+      </c>
+      <c r="E196" t="s">
+        <v>9</v>
+      </c>
+      <c r="F196" t="s">
+        <v>27</v>
+      </c>
+      <c r="G196" t="s">
+        <v>15</v>
+      </c>
+      <c r="H196" t="s">
+        <v>16</v>
+      </c>
+      <c r="I196" t="s">
+        <v>15</v>
+      </c>
+      <c r="J196" t="s">
+        <v>15</v>
+      </c>
+      <c r="K196" t="s">
+        <v>21</v>
+      </c>
+      <c r="L196" t="s">
+        <v>23</v>
+      </c>
+      <c r="M196" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>210</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1</v>
+      </c>
+      <c r="C197" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" t="s">
+        <v>8</v>
+      </c>
+      <c r="E197" t="s">
+        <v>9</v>
+      </c>
+      <c r="F197" t="s">
+        <v>12</v>
+      </c>
+      <c r="G197" t="s">
+        <v>15</v>
+      </c>
+      <c r="H197" t="s">
+        <v>16</v>
+      </c>
+      <c r="I197" t="s">
+        <v>15</v>
+      </c>
+      <c r="J197" t="s">
+        <v>15</v>
+      </c>
+      <c r="K197" t="s">
+        <v>20</v>
+      </c>
+      <c r="L197" t="s">
+        <v>22</v>
+      </c>
+      <c r="M197" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>211</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1</v>
+      </c>
+      <c r="C198" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" t="s">
+        <v>8</v>
+      </c>
+      <c r="E198" t="s">
+        <v>9</v>
+      </c>
+      <c r="F198" t="s">
+        <v>11</v>
+      </c>
+      <c r="G198" t="s">
+        <v>15</v>
+      </c>
+      <c r="H198" t="s">
+        <v>15</v>
+      </c>
+      <c r="I198" t="s">
+        <v>16</v>
+      </c>
+      <c r="J198" t="s">
+        <v>16</v>
+      </c>
+      <c r="K198" t="s">
+        <v>21</v>
+      </c>
+      <c r="L198" t="s">
+        <v>22</v>
+      </c>
+      <c r="M198" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>212</v>
+      </c>
+      <c r="B199" t="s">
+        <v>1</v>
+      </c>
+      <c r="C199" t="s">
+        <v>3</v>
+      </c>
+      <c r="D199" t="s">
+        <v>8</v>
+      </c>
+      <c r="E199" t="s">
+        <v>9</v>
+      </c>
+      <c r="F199" t="s">
+        <v>27</v>
+      </c>
+      <c r="G199" t="s">
+        <v>15</v>
+      </c>
+      <c r="H199" t="s">
+        <v>16</v>
+      </c>
+      <c r="I199" t="s">
+        <v>15</v>
+      </c>
+      <c r="J199" t="s">
+        <v>15</v>
+      </c>
+      <c r="K199" t="s">
+        <v>20</v>
+      </c>
+      <c r="L199" t="s">
+        <v>23</v>
+      </c>
+      <c r="M199" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="200" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>213</v>
+      </c>
+      <c r="B200" t="s">
+        <v>1</v>
+      </c>
+      <c r="C200" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" t="s">
+        <v>9</v>
+      </c>
+      <c r="E200" t="s">
+        <v>8</v>
+      </c>
+      <c r="F200" t="s">
+        <v>12</v>
+      </c>
+      <c r="G200" t="s">
+        <v>15</v>
+      </c>
+      <c r="H200" t="s">
+        <v>15</v>
+      </c>
+      <c r="I200" t="s">
+        <v>15</v>
+      </c>
+      <c r="J200" t="s">
+        <v>16</v>
+      </c>
+      <c r="K200" t="s">
+        <v>21</v>
+      </c>
+      <c r="L200" t="s">
+        <v>22</v>
+      </c>
+      <c r="M200" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="201" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>214</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1</v>
+      </c>
+      <c r="C201" t="s">
+        <v>3</v>
+      </c>
+      <c r="D201" t="s">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>9</v>
+      </c>
+      <c r="F201" t="s">
+        <v>11</v>
+      </c>
+      <c r="G201" t="s">
+        <v>15</v>
+      </c>
+      <c r="H201" t="s">
+        <v>15</v>
+      </c>
+      <c r="I201" t="s">
+        <v>15</v>
+      </c>
+      <c r="J201" t="s">
+        <v>16</v>
+      </c>
+      <c r="K201" t="s">
+        <v>20</v>
+      </c>
+      <c r="L201" t="s">
+        <v>23</v>
+      </c>
+      <c r="M201" t="s">
         <v>26</v>
       </c>
     </row>
